--- a/data/trans_orig/P17E-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P17E-Estudios-trans_orig.xlsx
@@ -538,7 +538,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2007</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2007 (tasa de respuesta: 100,0%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38809</t>
+          <t>38691</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>63628</t>
+          <t>65191</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,58%</t>
+          <t>11,55%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>18,99%</t>
+          <t>19,45%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52498</t>
+          <t>55014</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83291</t>
+          <t>85773</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>9,94%</t>
+          <t>10,42%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>15,77%</t>
+          <t>16,24%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>97779</t>
+          <t>100129</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>137807</t>
+          <t>139899</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,33%</t>
+          <t>11,6%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>15,97%</t>
+          <t>16,21%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>271480</t>
+          <t>269917</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>296299</t>
+          <t>296417</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>81,01%</t>
+          <t>80,55%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,42%</t>
+          <t>88,45%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>444779</t>
+          <t>442297</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>475572</t>
+          <t>473056</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>84,23%</t>
+          <t>83,76%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>90,06%</t>
+          <t>89,58%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>725371</t>
+          <t>723279</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>765399</t>
+          <t>763049</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>84,03%</t>
+          <t>83,79%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,67%</t>
+          <t>88,4%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40993</t>
+          <t>40635</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67125</t>
+          <t>67489</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>16,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,59%</t>
+          <t>26,74%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87828</t>
+          <t>87742</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>123205</t>
+          <t>122716</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,73%</t>
+          <t>21,71%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,48%</t>
+          <t>30,36%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>136737</t>
+          <t>137451</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>180089</t>
+          <t>180008</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,83%</t>
+          <t>20,93%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,43%</t>
+          <t>27,42%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>185300</t>
+          <t>184936</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211432</t>
+          <t>211790</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,41%</t>
+          <t>73,26%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>83,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>280947</t>
+          <t>281436</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316324</t>
+          <t>316410</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,52%</t>
+          <t>69,64%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,27%</t>
+          <t>78,29%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>476488</t>
+          <t>476569</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>519840</t>
+          <t>519126</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,57%</t>
+          <t>72,58%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,17%</t>
+          <t>79,07%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18027</t>
+          <t>18609</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>35647</t>
+          <t>36305</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,12%</t>
+          <t>25,93%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>49,67%</t>
+          <t>50,59%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28955</t>
+          <t>27989</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49124</t>
+          <t>48962</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,93%</t>
+          <t>24,1%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,29%</t>
+          <t>42,15%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51888</t>
+          <t>51812</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>79021</t>
+          <t>78509</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,61%</t>
+          <t>27,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>42,05%</t>
+          <t>41,78%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>36122</t>
+          <t>35464</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53742</t>
+          <t>53160</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>50,33%</t>
+          <t>49,41%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,88%</t>
+          <t>74,07%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67024</t>
+          <t>67186</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87193</t>
+          <t>88159</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,71%</t>
+          <t>57,85%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,07%</t>
+          <t>75,9%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>108895</t>
+          <t>109407</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136028</t>
+          <t>136104</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>57,95%</t>
+          <t>58,22%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,39%</t>
+          <t>72,43%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>112176</t>
+          <t>110379</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>151915</t>
+          <t>151942</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,01%</t>
+          <t>16,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,04%</t>
+          <t>23,05%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>182290</t>
+          <t>186456</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>238856</t>
+          <t>238596</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,39%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,78%</t>
+          <t>22,76%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>309304</t>
+          <t>307022</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>375223</t>
+          <t>373086</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>18,11%</t>
+          <t>17,98%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>21,85%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>507387</t>
+          <t>507360</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>547126</t>
+          <t>548923</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,96%</t>
+          <t>76,95%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,99%</t>
+          <t>83,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>809514</t>
+          <t>809774</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>866080</t>
+          <t>861914</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,22%</t>
+          <t>77,24%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,61%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1332449</t>
+          <t>1334586</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1398368</t>
+          <t>1400650</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>78,15%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>81,89%</t>
+          <t>82,02%</t>
         </is>
       </c>
     </row>
@@ -2141,7 +2141,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2012</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2012 (tasa de respuesta: 99,89%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61562</t>
+          <t>61269</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>92481</t>
+          <t>93627</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,88%</t>
+          <t>17,79%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,85%</t>
+          <t>27,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67705</t>
+          <t>67869</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>101829</t>
+          <t>102061</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,3%</t>
+          <t>12,33%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,5%</t>
+          <t>18,54%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>138188</t>
+          <t>135352</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>181282</t>
+          <t>181838</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,44%</t>
+          <t>15,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,26%</t>
+          <t>20,32%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>251923</t>
+          <t>250777</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>282842</t>
+          <t>283135</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,15%</t>
+          <t>72,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,12%</t>
+          <t>82,21%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>448568</t>
+          <t>448336</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>482692</t>
+          <t>482528</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,5%</t>
+          <t>81,46%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,7%</t>
+          <t>87,67%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>713520</t>
+          <t>712964</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>756614</t>
+          <t>759450</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,74%</t>
+          <t>79,68%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,56%</t>
+          <t>84,87%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>52574</t>
+          <t>51496</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82748</t>
+          <t>82597</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,65%</t>
+          <t>14,35%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,06%</t>
+          <t>23,02%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82642</t>
+          <t>82510</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>116783</t>
+          <t>117134</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,67%</t>
+          <t>23,74%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>143175</t>
+          <t>142507</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>190174</t>
+          <t>190597</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,12 +2764,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,8%</t>
+          <t>16,72%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>22,32%</t>
+          <t>22,37%</t>
         </is>
       </c>
     </row>
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>276023</t>
+          <t>276174</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>306197</t>
+          <t>307275</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,94%</t>
+          <t>76,98%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,35%</t>
+          <t>85,65%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>376578</t>
+          <t>376227</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>410719</t>
+          <t>410851</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,33%</t>
+          <t>76,26%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>83,28%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>661958</t>
+          <t>661535</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>708957</t>
+          <t>709625</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2877,12 +2877,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>77,68%</t>
+          <t>77,63%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,2%</t>
+          <t>83,28%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12576</t>
+          <t>12876</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29199</t>
+          <t>29202</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,7 +3037,7 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,56%</t>
+          <t>16,96%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21212</t>
+          <t>21726</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>42473</t>
+          <t>40966</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>19,52%</t>
+          <t>20,0%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>39,09%</t>
+          <t>37,7%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39948</t>
+          <t>39803</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>65779</t>
+          <t>66009</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,56%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,63%</t>
+          <t>35,76%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46744</t>
+          <t>46741</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63367</t>
+          <t>63067</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3155,7 +3155,7 @@
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,44%</t>
+          <t>83,04%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>66175</t>
+          <t>67682</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>87436</t>
+          <t>86922</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>60,91%</t>
+          <t>62,3%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,48%</t>
+          <t>80,0%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118812</t>
+          <t>118582</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144643</t>
+          <t>144788</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,37%</t>
+          <t>64,24%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,44%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>140853</t>
+          <t>139926</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>190012</t>
+          <t>185030</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>18,08%</t>
+          <t>17,96%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>24,39%</t>
+          <t>23,75%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>187738</t>
+          <t>187214</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>239750</t>
+          <t>241002</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,12 +3415,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,29%</t>
+          <t>16,25%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>20,8%</t>
+          <t>20,91%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>342164</t>
+          <t>340893</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>414708</t>
+          <t>412005</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,71%</t>
+          <t>17,65%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,47%</t>
+          <t>21,33%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>589106</t>
+          <t>594088</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>638265</t>
+          <t>639192</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>75,61%</t>
+          <t>76,25%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>81,92%</t>
+          <t>82,04%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>912657</t>
+          <t>911405</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>964669</t>
+          <t>965193</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3528,12 +3528,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>79,2%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,71%</t>
+          <t>83,75%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1516817</t>
+          <t>1519520</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1589361</t>
+          <t>1590632</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,53%</t>
+          <t>78,67%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,29%</t>
+          <t>82,35%</t>
         </is>
       </c>
     </row>
@@ -3744,7 +3744,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2016</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2016 (tasa de respuesta: 99,79%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>29141</t>
+          <t>30021</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>52899</t>
+          <t>51571</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,2%</t>
+          <t>11,54%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>20,33%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52499</t>
+          <t>52646</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>84025</t>
+          <t>83509</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,46%</t>
+          <t>12,5%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,95%</t>
+          <t>19,82%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>87284</t>
+          <t>88540</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>127940</t>
+          <t>128271</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,81%</t>
+          <t>12,99%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,78%</t>
+          <t>18,82%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>207265</t>
+          <t>208593</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>231023</t>
+          <t>230143</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>79,67%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,8%</t>
+          <t>88,46%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>337207</t>
+          <t>337723</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>368733</t>
+          <t>368586</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,05%</t>
+          <t>80,18%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,54%</t>
+          <t>87,5%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>553456</t>
+          <t>553125</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>594112</t>
+          <t>592856</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,22%</t>
+          <t>81,18%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,19%</t>
+          <t>87,01%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>67506</t>
+          <t>64396</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100954</t>
+          <t>100045</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,47%</t>
+          <t>13,8%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,64%</t>
+          <t>21,45%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95366</t>
+          <t>95697</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>131351</t>
+          <t>133638</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,0%</t>
+          <t>16,05%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,03%</t>
+          <t>22,42%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>170319</t>
+          <t>171017</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>221947</t>
+          <t>224669</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,03%</t>
+          <t>16,09%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>20,89%</t>
+          <t>21,14%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>365560</t>
+          <t>366469</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>399008</t>
+          <t>402118</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,36%</t>
+          <t>78,55%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,53%</t>
+          <t>86,2%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>464830</t>
+          <t>462543</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500815</t>
+          <t>500484</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,97%</t>
+          <t>77,58%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,0%</t>
+          <t>83,95%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>840748</t>
+          <t>838026</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>892376</t>
+          <t>891678</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>79,11%</t>
+          <t>78,86%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,97%</t>
+          <t>83,91%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24780</t>
+          <t>24139</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45598</t>
+          <t>45442</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,7%</t>
+          <t>20,17%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,09%</t>
+          <t>37,96%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>29194</t>
+          <t>28592</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>49803</t>
+          <t>50491</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>21,06%</t>
+          <t>20,63%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>35,93%</t>
+          <t>36,42%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58617</t>
+          <t>58968</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>89539</t>
+          <t>88225</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,69%</t>
+          <t>22,83%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,66%</t>
+          <t>34,15%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74107</t>
+          <t>74263</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>94925</t>
+          <t>95566</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,91%</t>
+          <t>62,04%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,3%</t>
+          <t>79,83%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88820</t>
+          <t>88132</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>109429</t>
+          <t>110031</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>64,07%</t>
+          <t>63,58%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>78,94%</t>
+          <t>79,37%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>168789</t>
+          <t>170103</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>199711</t>
+          <t>199360</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,34%</t>
+          <t>65,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,31%</t>
+          <t>77,17%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>133697</t>
+          <t>133964</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>180178</t>
+          <t>180915</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,12 +4983,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,8%</t>
+          <t>15,83%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>21,29%</t>
+          <t>21,38%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>194707</t>
+          <t>194431</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>249506</t>
+          <t>247365</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,84%</t>
+          <t>16,82%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,58%</t>
+          <t>21,4%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>339626</t>
+          <t>339840</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>409252</t>
+          <t>411237</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>16,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,44%</t>
+          <t>20,54%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>666205</t>
+          <t>665468</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>712686</t>
+          <t>712419</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5096,12 +5096,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>78,71%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,2%</t>
+          <t>84,17%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>906530</t>
+          <t>908671</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>961329</t>
+          <t>961605</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,42%</t>
+          <t>78,6%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,16%</t>
+          <t>83,18%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1593167</t>
+          <t>1591182</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1662793</t>
+          <t>1662579</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,56%</t>
+          <t>79,46%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>83,03%</t>
         </is>
       </c>
     </row>
@@ -5347,7 +5347,7 @@
     <row r="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t>Población según era el médico al que consultó en la última visita en 2023</t>
+          <t>Población según el/a médico/a al que visitó en la última consulta médica realizada en las últimas 2 semanas en 2023 (tasa de respuesta: 99,85%)</t>
         </is>
       </c>
       <c r="B1" s="2" t="n"/>
@@ -5542,12 +5542,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>19648</t>
+          <t>20077</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>35903</t>
+          <t>36697</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -5557,12 +5557,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,44%</t>
+          <t>14,75%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,38%</t>
+          <t>26,96%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25212</t>
+          <t>25370</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>40906</t>
+          <t>41897</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -5592,12 +5592,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,61%</t>
+          <t>10,68%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,22%</t>
+          <t>17,63%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5612,12 +5612,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>48641</t>
+          <t>49585</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>71342</t>
+          <t>72856</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -5627,12 +5627,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,02%</t>
+          <t>13,27%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,09%</t>
+          <t>19,5%</t>
         </is>
       </c>
     </row>
@@ -5655,12 +5655,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>100208</t>
+          <t>99414</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116463</t>
+          <t>116034</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -5670,12 +5670,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,62%</t>
+          <t>73,04%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,56%</t>
+          <t>85,25%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5690,12 +5690,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>196696</t>
+          <t>195705</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>212390</t>
+          <t>212232</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -5705,12 +5705,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,78%</t>
+          <t>82,37%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,39%</t>
+          <t>89,32%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5725,12 +5725,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>302371</t>
+          <t>300857</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>325072</t>
+          <t>324128</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -5740,12 +5740,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,91%</t>
+          <t>80,5%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,98%</t>
+          <t>86,73%</t>
         </is>
       </c>
     </row>
@@ -5885,12 +5885,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70289</t>
+          <t>70612</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>107490</t>
+          <t>104944</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -5900,12 +5900,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,01%</t>
+          <t>19,1%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>29,08%</t>
+          <t>28,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5920,12 +5920,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>69932</t>
+          <t>75822</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140090</t>
+          <t>140735</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -5935,12 +5935,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>13,94%</t>
+          <t>15,12%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>27,93%</t>
+          <t>28,06%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5955,12 +5955,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>145943</t>
+          <t>150360</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>228299</t>
+          <t>231549</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -5970,12 +5970,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,75%</t>
+          <t>17,26%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,2%</t>
+          <t>26,58%</t>
         </is>
       </c>
     </row>
@@ -5998,12 +5998,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>262168</t>
+          <t>264714</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>299369</t>
+          <t>299046</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -6013,12 +6013,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>70,92%</t>
+          <t>71,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,99%</t>
+          <t>80,9%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6033,12 +6033,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>361526</t>
+          <t>360881</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>431684</t>
+          <t>425794</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -6048,12 +6048,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>72,07%</t>
+          <t>71,94%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>86,06%</t>
+          <t>84,88%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6068,12 +6068,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>642975</t>
+          <t>639725</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>725331</t>
+          <t>720914</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -6083,12 +6083,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,8%</t>
+          <t>73,42%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,25%</t>
+          <t>82,74%</t>
         </is>
       </c>
     </row>
@@ -6228,12 +6228,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29074</t>
+          <t>29200</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>51083</t>
+          <t>50702</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -6243,12 +6243,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>21,97%</t>
+          <t>22,06%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,6%</t>
+          <t>38,31%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6263,12 +6263,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>38070</t>
+          <t>37419</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>58976</t>
+          <t>57698</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -6278,12 +6278,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,81%</t>
+          <t>24,38%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>38,43%</t>
+          <t>37,6%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6298,12 +6298,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>71584</t>
+          <t>73080</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102885</t>
+          <t>102233</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -6313,12 +6313,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,05%</t>
+          <t>25,57%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>36,0%</t>
+          <t>35,77%</t>
         </is>
       </c>
     </row>
@@ -6341,12 +6341,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81273</t>
+          <t>81654</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103282</t>
+          <t>103156</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -6356,12 +6356,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,4%</t>
+          <t>61,69%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>78,03%</t>
+          <t>77,94%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6376,12 +6376,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>94480</t>
+          <t>95758</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>115386</t>
+          <t>116037</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -6391,12 +6391,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>61,57%</t>
+          <t>62,4%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,19%</t>
+          <t>75,62%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6411,12 +6411,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>182927</t>
+          <t>183579</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>214228</t>
+          <t>212732</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -6426,12 +6426,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,0%</t>
+          <t>64,23%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,95%</t>
+          <t>74,43%</t>
         </is>
       </c>
     </row>
@@ -6571,12 +6571,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>134052</t>
+          <t>132347</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>177145</t>
+          <t>179585</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -6586,12 +6586,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>21,01%</t>
+          <t>20,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>27,76%</t>
+          <t>28,14%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6606,12 +6606,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>148459</t>
+          <t>148122</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>220787</t>
+          <t>218974</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -6621,12 +6621,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,63%</t>
+          <t>16,59%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,73%</t>
+          <t>24,53%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6641,12 +6641,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>297743</t>
+          <t>294403</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>383102</t>
+          <t>379586</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -6656,12 +6656,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,23%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>25,03%</t>
+          <t>24,8%</t>
         </is>
       </c>
     </row>
@@ -6684,12 +6684,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>460980</t>
+          <t>458540</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>504073</t>
+          <t>505778</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -6699,12 +6699,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>72,24%</t>
+          <t>71,86%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>78,99%</t>
+          <t>79,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6719,12 +6719,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>671887</t>
+          <t>673700</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>744215</t>
+          <t>744552</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -6734,12 +6734,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,27%</t>
+          <t>75,47%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,37%</t>
+          <t>83,41%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6754,12 +6754,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1147698</t>
+          <t>1151214</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1233057</t>
+          <t>1236397</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -6769,12 +6769,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>74,97%</t>
+          <t>75,2%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,77%</t>
         </is>
       </c>
     </row>

--- a/data/trans_orig/P17E-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P17E-Estudios-trans_orig.xlsx
@@ -733,12 +733,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>38691</t>
+          <t>39618</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>65191</t>
+          <t>63700</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -748,12 +748,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,55%</t>
+          <t>11,82%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,45%</t>
+          <t>19,01%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -768,12 +768,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>55014</t>
+          <t>53140</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>85773</t>
+          <t>83624</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -783,12 +783,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,42%</t>
+          <t>10,06%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>16,24%</t>
+          <t>15,84%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -803,12 +803,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>100129</t>
+          <t>99920</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>139899</t>
+          <t>138925</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -818,12 +818,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>11,6%</t>
+          <t>11,58%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>16,21%</t>
+          <t>16,09%</t>
         </is>
       </c>
     </row>
@@ -846,12 +846,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>269917</t>
+          <t>271408</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>296417</t>
+          <t>295490</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -861,12 +861,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,55%</t>
+          <t>80,99%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,45%</t>
+          <t>88,18%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -881,12 +881,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>442297</t>
+          <t>444446</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>473056</t>
+          <t>474930</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -896,12 +896,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>83,76%</t>
+          <t>84,16%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,58%</t>
+          <t>89,94%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -916,12 +916,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>723279</t>
+          <t>724253</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>763049</t>
+          <t>763258</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -931,12 +931,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>83,79%</t>
+          <t>83,91%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>88,4%</t>
+          <t>88,42%</t>
         </is>
       </c>
     </row>
@@ -1076,12 +1076,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>40635</t>
+          <t>40133</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>67489</t>
+          <t>66074</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -1091,12 +1091,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>16,1%</t>
+          <t>15,9%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>26,74%</t>
+          <t>26,18%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -1111,12 +1111,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>87742</t>
+          <t>87181</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>122716</t>
+          <t>123933</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -1126,12 +1126,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>21,71%</t>
+          <t>21,57%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>30,36%</t>
+          <t>30,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -1146,12 +1146,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>137451</t>
+          <t>136659</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>180008</t>
+          <t>180482</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -1161,12 +1161,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>20,93%</t>
+          <t>20,81%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>27,42%</t>
+          <t>27,49%</t>
         </is>
       </c>
     </row>
@@ -1189,12 +1189,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>184936</t>
+          <t>186351</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>211790</t>
+          <t>212292</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -1204,12 +1204,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>73,26%</t>
+          <t>73,82%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>83,9%</t>
+          <t>84,1%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -1224,12 +1224,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>281436</t>
+          <t>280219</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>316410</t>
+          <t>316971</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -1239,12 +1239,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>69,64%</t>
+          <t>69,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>78,29%</t>
+          <t>78,43%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -1259,12 +1259,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>476569</t>
+          <t>476095</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>519126</t>
+          <t>519918</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -1274,12 +1274,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>72,58%</t>
+          <t>72,51%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>79,07%</t>
+          <t>79,19%</t>
         </is>
       </c>
     </row>
@@ -1419,12 +1419,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>18609</t>
+          <t>18842</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>36305</t>
+          <t>36593</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -1434,12 +1434,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>25,93%</t>
+          <t>26,25%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>50,59%</t>
+          <t>50,99%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -1454,12 +1454,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>27989</t>
+          <t>28582</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>48962</t>
+          <t>48995</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -1469,12 +1469,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,61%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>42,15%</t>
+          <t>42,18%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -1489,12 +1489,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>51812</t>
+          <t>52771</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>78509</t>
+          <t>79493</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -1504,12 +1504,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>27,57%</t>
+          <t>28,08%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>41,78%</t>
+          <t>42,3%</t>
         </is>
       </c>
     </row>
@@ -1532,12 +1532,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>35464</t>
+          <t>35176</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>53160</t>
+          <t>52927</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -1547,12 +1547,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>49,41%</t>
+          <t>49,01%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>74,07%</t>
+          <t>73,75%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -1567,12 +1567,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67186</t>
+          <t>67153</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>88159</t>
+          <t>87566</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -1582,12 +1582,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>57,85%</t>
+          <t>57,82%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,39%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -1602,12 +1602,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>109407</t>
+          <t>108423</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>136104</t>
+          <t>135145</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -1617,12 +1617,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>58,22%</t>
+          <t>57,7%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>72,43%</t>
+          <t>71,92%</t>
         </is>
       </c>
     </row>
@@ -1762,12 +1762,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>110379</t>
+          <t>111032</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>151942</t>
+          <t>151224</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -1777,12 +1777,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>16,74%</t>
+          <t>16,84%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,05%</t>
+          <t>22,94%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -1797,12 +1797,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>186456</t>
+          <t>187574</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>238596</t>
+          <t>237650</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -1812,12 +1812,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,89%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>22,76%</t>
+          <t>22,67%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -1832,12 +1832,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>307022</t>
+          <t>306808</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>373086</t>
+          <t>373335</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -1847,12 +1847,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,98%</t>
+          <t>17,97%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,85%</t>
+          <t>21,86%</t>
         </is>
       </c>
     </row>
@@ -1875,12 +1875,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>507360</t>
+          <t>508078</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>548923</t>
+          <t>548270</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -1890,12 +1890,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,95%</t>
+          <t>77,06%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>83,26%</t>
+          <t>83,16%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -1910,12 +1910,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>809774</t>
+          <t>810720</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>861914</t>
+          <t>860796</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -1925,12 +1925,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>77,24%</t>
+          <t>77,33%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,11%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -1945,12 +1945,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1334586</t>
+          <t>1334337</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1400650</t>
+          <t>1400864</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -1960,12 +1960,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,15%</t>
+          <t>78,14%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,02%</t>
+          <t>82,03%</t>
         </is>
       </c>
     </row>
@@ -2336,12 +2336,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>61269</t>
+          <t>61638</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>93627</t>
+          <t>93875</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -2351,12 +2351,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>17,79%</t>
+          <t>17,9%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>27,19%</t>
+          <t>27,26%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -2371,12 +2371,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>67869</t>
+          <t>66910</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>102061</t>
+          <t>101141</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -2386,12 +2386,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,33%</t>
+          <t>12,16%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>18,54%</t>
+          <t>18,38%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -2406,12 +2406,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>135352</t>
+          <t>137231</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>181838</t>
+          <t>187130</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -2421,12 +2421,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>15,13%</t>
+          <t>15,34%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>20,32%</t>
+          <t>20,91%</t>
         </is>
       </c>
     </row>
@@ -2449,12 +2449,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>250777</t>
+          <t>250529</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>283135</t>
+          <t>282766</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -2464,12 +2464,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>72,81%</t>
+          <t>72,74%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>82,21%</t>
+          <t>82,1%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -2484,12 +2484,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>448336</t>
+          <t>449256</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>482528</t>
+          <t>483487</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -2499,12 +2499,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>81,46%</t>
+          <t>81,62%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,67%</t>
+          <t>87,84%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -2519,12 +2519,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>712964</t>
+          <t>707672</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>759450</t>
+          <t>757571</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -2534,12 +2534,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>79,68%</t>
+          <t>79,09%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>84,87%</t>
+          <t>84,66%</t>
         </is>
       </c>
     </row>
@@ -2679,12 +2679,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>51496</t>
+          <t>53626</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>82597</t>
+          <t>84660</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -2694,12 +2694,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>14,35%</t>
+          <t>14,95%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>23,02%</t>
+          <t>23,6%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -2714,12 +2714,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>82510</t>
+          <t>81272</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>117134</t>
+          <t>116710</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -2729,12 +2729,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,47%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>23,74%</t>
+          <t>23,66%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -2749,12 +2749,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>142507</t>
+          <t>144394</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>190597</t>
+          <t>190662</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -2764,7 +2764,7 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,72%</t>
+          <t>16,94%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
@@ -2792,12 +2792,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>276174</t>
+          <t>274111</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>307275</t>
+          <t>305145</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -2807,12 +2807,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>76,98%</t>
+          <t>76,4%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>85,65%</t>
+          <t>85,05%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -2827,12 +2827,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>376227</t>
+          <t>376651</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>410851</t>
+          <t>412089</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -2842,12 +2842,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>76,26%</t>
+          <t>76,34%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,53%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -2862,12 +2862,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>661535</t>
+          <t>661470</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>709625</t>
+          <t>707738</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -2882,7 +2882,7 @@
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,28%</t>
+          <t>83,06%</t>
         </is>
       </c>
     </row>
@@ -3022,12 +3022,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>12876</t>
+          <t>12094</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>29202</t>
+          <t>29242</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -3037,12 +3037,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>16,96%</t>
+          <t>15,92%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,45%</t>
+          <t>38,51%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -3057,12 +3057,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>21726</t>
+          <t>22754</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>40966</t>
+          <t>41665</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -3072,12 +3072,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,0%</t>
+          <t>20,94%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,7%</t>
+          <t>38,35%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -3092,12 +3092,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>39803</t>
+          <t>39157</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>66009</t>
+          <t>64887</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -3107,12 +3107,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>21,56%</t>
+          <t>21,21%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,76%</t>
+          <t>35,15%</t>
         </is>
       </c>
     </row>
@@ -3135,12 +3135,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>46741</t>
+          <t>46701</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>63067</t>
+          <t>63849</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -3150,12 +3150,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,55%</t>
+          <t>61,49%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>83,04%</t>
+          <t>84,08%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -3170,12 +3170,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>67682</t>
+          <t>66983</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>86922</t>
+          <t>85894</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -3185,12 +3185,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,3%</t>
+          <t>61,65%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>80,0%</t>
+          <t>79,06%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -3205,12 +3205,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>118582</t>
+          <t>119704</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>144788</t>
+          <t>145434</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -3220,12 +3220,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,24%</t>
+          <t>64,85%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>78,44%</t>
+          <t>78,79%</t>
         </is>
       </c>
     </row>
@@ -3365,12 +3365,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>139926</t>
+          <t>141517</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>185030</t>
+          <t>187262</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -3380,12 +3380,12 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>17,96%</t>
+          <t>18,16%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>23,75%</t>
+          <t>24,04%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -3400,12 +3400,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>187214</t>
+          <t>189410</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>241002</t>
+          <t>240990</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -3415,7 +3415,7 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,25%</t>
+          <t>16,44%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
@@ -3435,12 +3435,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>340893</t>
+          <t>338917</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>412005</t>
+          <t>413005</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -3450,12 +3450,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>17,65%</t>
+          <t>17,55%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>21,33%</t>
+          <t>21,38%</t>
         </is>
       </c>
     </row>
@@ -3478,12 +3478,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>594088</t>
+          <t>591856</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>639192</t>
+          <t>637601</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -3493,12 +3493,12 @@
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>76,25%</t>
+          <t>75,96%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>82,04%</t>
+          <t>81,84%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -3513,12 +3513,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>911405</t>
+          <t>911417</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>965193</t>
+          <t>962997</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -3533,7 +3533,7 @@
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,75%</t>
+          <t>83,56%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -3548,12 +3548,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1519520</t>
+          <t>1518520</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1590632</t>
+          <t>1592608</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -3563,12 +3563,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>78,67%</t>
+          <t>78,62%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>82,35%</t>
+          <t>82,45%</t>
         </is>
       </c>
     </row>
@@ -3939,12 +3939,12 @@
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>30021</t>
+          <t>29951</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>51571</t>
+          <t>51411</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
@@ -3954,12 +3954,12 @@
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>11,54%</t>
+          <t>11,51%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>19,76%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -3974,12 +3974,12 @@
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>52646</t>
+          <t>54023</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>83509</t>
+          <t>84989</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
@@ -3989,12 +3989,12 @@
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>12,5%</t>
+          <t>12,83%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>19,82%</t>
+          <t>20,18%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -4009,12 +4009,12 @@
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>88540</t>
+          <t>89446</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>128271</t>
+          <t>128691</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
@@ -4024,12 +4024,12 @@
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>12,99%</t>
+          <t>13,13%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>18,82%</t>
+          <t>18,89%</t>
         </is>
       </c>
     </row>
@@ -4052,12 +4052,12 @@
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>208593</t>
+          <t>208753</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>230143</t>
+          <t>230213</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
@@ -4067,12 +4067,12 @@
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>80,24%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>88,46%</t>
+          <t>88,49%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -4087,12 +4087,12 @@
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>337723</t>
+          <t>336243</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>368586</t>
+          <t>367209</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
@@ -4102,12 +4102,12 @@
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>80,18%</t>
+          <t>79,82%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>87,5%</t>
+          <t>87,17%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -4122,12 +4122,12 @@
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>553125</t>
+          <t>552705</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>592856</t>
+          <t>591950</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
@@ -4137,12 +4137,12 @@
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>81,18%</t>
+          <t>81,11%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>87,01%</t>
+          <t>86,87%</t>
         </is>
       </c>
     </row>
@@ -4282,12 +4282,12 @@
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>64396</t>
+          <t>67106</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>100045</t>
+          <t>99773</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
@@ -4297,12 +4297,12 @@
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>13,8%</t>
+          <t>14,38%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>21,45%</t>
+          <t>21,39%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -4317,12 +4317,12 @@
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>95697</t>
+          <t>94965</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>133638</t>
+          <t>134639</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
@@ -4332,12 +4332,12 @@
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>16,05%</t>
+          <t>15,93%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>22,42%</t>
+          <t>22,58%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -4352,12 +4352,12 @@
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>171017</t>
+          <t>171549</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>224669</t>
+          <t>223386</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
@@ -4367,12 +4367,12 @@
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>16,09%</t>
+          <t>16,14%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>21,14%</t>
+          <t>21,02%</t>
         </is>
       </c>
     </row>
@@ -4395,12 +4395,12 @@
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>366469</t>
+          <t>366741</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>402118</t>
+          <t>399408</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
@@ -4410,12 +4410,12 @@
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>78,55%</t>
+          <t>78,61%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>86,2%</t>
+          <t>85,62%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -4430,12 +4430,12 @@
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>462543</t>
+          <t>461542</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>500484</t>
+          <t>501216</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
@@ -4445,12 +4445,12 @@
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>77,58%</t>
+          <t>77,42%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>83,95%</t>
+          <t>84,07%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -4465,12 +4465,12 @@
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>838026</t>
+          <t>839309</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>891678</t>
+          <t>891146</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
@@ -4480,12 +4480,12 @@
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>78,86%</t>
+          <t>78,98%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>83,91%</t>
+          <t>83,86%</t>
         </is>
       </c>
     </row>
@@ -4625,12 +4625,12 @@
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>24139</t>
+          <t>24637</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>45442</t>
+          <t>46205</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
@@ -4640,12 +4640,12 @@
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>20,17%</t>
+          <t>20,58%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>37,96%</t>
+          <t>38,6%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -4660,12 +4660,12 @@
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>28592</t>
+          <t>27375</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>50491</t>
+          <t>49964</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
@@ -4675,12 +4675,12 @@
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>20,63%</t>
+          <t>19,75%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>36,42%</t>
+          <t>36,04%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -4695,12 +4695,12 @@
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>58968</t>
+          <t>58731</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>88225</t>
+          <t>89073</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
@@ -4710,12 +4710,12 @@
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>22,83%</t>
+          <t>22,74%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>34,15%</t>
+          <t>34,48%</t>
         </is>
       </c>
     </row>
@@ -4738,12 +4738,12 @@
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>74263</t>
+          <t>73500</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>95566</t>
+          <t>95068</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>62,04%</t>
+          <t>61,4%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>79,83%</t>
+          <t>79,42%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -4773,12 +4773,12 @@
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>88132</t>
+          <t>88659</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>110031</t>
+          <t>111248</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
@@ -4788,12 +4788,12 @@
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>63,58%</t>
+          <t>63,96%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>79,37%</t>
+          <t>80,25%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -4808,12 +4808,12 @@
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>170103</t>
+          <t>169255</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>199360</t>
+          <t>199597</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
@@ -4823,12 +4823,12 @@
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>65,85%</t>
+          <t>65,52%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>77,17%</t>
+          <t>77,26%</t>
         </is>
       </c>
     </row>
@@ -4968,12 +4968,12 @@
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>133964</t>
+          <t>133215</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>180915</t>
+          <t>180972</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
@@ -4983,7 +4983,7 @@
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>15,83%</t>
+          <t>15,74%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
@@ -5003,12 +5003,12 @@
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>194431</t>
+          <t>190654</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>247365</t>
+          <t>247515</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
@@ -5018,12 +5018,12 @@
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,82%</t>
+          <t>16,49%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>21,4%</t>
+          <t>21,41%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -5038,12 +5038,12 @@
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>339840</t>
+          <t>338333</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>411237</t>
+          <t>412475</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
@@ -5053,12 +5053,12 @@
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>16,97%</t>
+          <t>16,9%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>20,54%</t>
+          <t>20,6%</t>
         </is>
       </c>
     </row>
@@ -5081,12 +5081,12 @@
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>665468</t>
+          <t>665411</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>712419</t>
+          <t>713168</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>84,17%</t>
+          <t>84,26%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>908671</t>
+          <t>908521</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>961605</t>
+          <t>965382</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
@@ -5131,12 +5131,12 @@
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>78,6%</t>
+          <t>78,59%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,18%</t>
+          <t>83,51%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -5151,12 +5151,12 @@
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1591182</t>
+          <t>1589944</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1662579</t>
+          <t>1664086</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
@@ -5166,12 +5166,12 @@
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>79,46%</t>
+          <t>79,4%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>83,03%</t>
+          <t>83,1%</t>
         </is>
       </c>
     </row>
@@ -5537,32 +5537,32 @@
       </c>
       <c r="D4" s="2" t="inlineStr">
         <is>
-          <t>27090</t>
+          <t>28630</t>
         </is>
       </c>
       <c r="E4" s="2" t="inlineStr">
         <is>
-          <t>20077</t>
+          <t>20825</t>
         </is>
       </c>
       <c r="F4" s="2" t="inlineStr">
         <is>
-          <t>36697</t>
+          <t>38153</t>
         </is>
       </c>
       <c r="G4" s="2" t="inlineStr">
         <is>
-          <t>19,9%</t>
+          <t>19,65%</t>
         </is>
       </c>
       <c r="H4" s="2" t="inlineStr">
         <is>
-          <t>14,75%</t>
+          <t>14,3%</t>
         </is>
       </c>
       <c r="I4" s="2" t="inlineStr">
         <is>
-          <t>26,96%</t>
+          <t>26,19%</t>
         </is>
       </c>
       <c r="J4" s="2" t="inlineStr">
@@ -5572,32 +5572,32 @@
       </c>
       <c r="K4" s="2" t="inlineStr">
         <is>
-          <t>32754</t>
+          <t>35714</t>
         </is>
       </c>
       <c r="L4" s="2" t="inlineStr">
         <is>
-          <t>25370</t>
+          <t>27764</t>
         </is>
       </c>
       <c r="M4" s="2" t="inlineStr">
         <is>
-          <t>41897</t>
+          <t>44549</t>
         </is>
       </c>
       <c r="N4" s="2" t="inlineStr">
         <is>
-          <t>13,79%</t>
+          <t>13,88%</t>
         </is>
       </c>
       <c r="O4" s="2" t="inlineStr">
         <is>
-          <t>10,68%</t>
+          <t>10,79%</t>
         </is>
       </c>
       <c r="P4" s="2" t="inlineStr">
         <is>
-          <t>17,63%</t>
+          <t>17,31%</t>
         </is>
       </c>
       <c r="Q4" s="2" t="inlineStr">
@@ -5607,32 +5607,32 @@
       </c>
       <c r="R4" s="2" t="inlineStr">
         <is>
-          <t>59844</t>
+          <t>64343</t>
         </is>
       </c>
       <c r="S4" s="2" t="inlineStr">
         <is>
-          <t>49585</t>
+          <t>52209</t>
         </is>
       </c>
       <c r="T4" s="2" t="inlineStr">
         <is>
-          <t>72856</t>
+          <t>76868</t>
         </is>
       </c>
       <c r="U4" s="2" t="inlineStr">
         <is>
-          <t>16,01%</t>
+          <t>15,97%</t>
         </is>
       </c>
       <c r="V4" s="2" t="inlineStr">
         <is>
-          <t>13,27%</t>
+          <t>12,96%</t>
         </is>
       </c>
       <c r="W4" s="2" t="inlineStr">
         <is>
-          <t>19,5%</t>
+          <t>19,07%</t>
         </is>
       </c>
     </row>
@@ -5650,32 +5650,32 @@
       </c>
       <c r="D5" s="2" t="inlineStr">
         <is>
-          <t>109021</t>
+          <t>117044</t>
         </is>
       </c>
       <c r="E5" s="2" t="inlineStr">
         <is>
-          <t>99414</t>
+          <t>107521</t>
         </is>
       </c>
       <c r="F5" s="2" t="inlineStr">
         <is>
-          <t>116034</t>
+          <t>124849</t>
         </is>
       </c>
       <c r="G5" s="2" t="inlineStr">
         <is>
-          <t>80,1%</t>
+          <t>80,35%</t>
         </is>
       </c>
       <c r="H5" s="2" t="inlineStr">
         <is>
-          <t>73,04%</t>
+          <t>73,81%</t>
         </is>
       </c>
       <c r="I5" s="2" t="inlineStr">
         <is>
-          <t>85,25%</t>
+          <t>85,7%</t>
         </is>
       </c>
       <c r="J5" s="2" t="inlineStr">
@@ -5685,32 +5685,32 @@
       </c>
       <c r="K5" s="2" t="inlineStr">
         <is>
-          <t>204848</t>
+          <t>221601</t>
         </is>
       </c>
       <c r="L5" s="2" t="inlineStr">
         <is>
-          <t>195705</t>
+          <t>212766</t>
         </is>
       </c>
       <c r="M5" s="2" t="inlineStr">
         <is>
-          <t>212232</t>
+          <t>229551</t>
         </is>
       </c>
       <c r="N5" s="2" t="inlineStr">
         <is>
-          <t>86,21%</t>
+          <t>86,12%</t>
         </is>
       </c>
       <c r="O5" s="2" t="inlineStr">
         <is>
-          <t>82,37%</t>
+          <t>82,69%</t>
         </is>
       </c>
       <c r="P5" s="2" t="inlineStr">
         <is>
-          <t>89,32%</t>
+          <t>89,21%</t>
         </is>
       </c>
       <c r="Q5" s="2" t="inlineStr">
@@ -5720,32 +5720,32 @@
       </c>
       <c r="R5" s="2" t="inlineStr">
         <is>
-          <t>313869</t>
+          <t>338645</t>
         </is>
       </c>
       <c r="S5" s="2" t="inlineStr">
         <is>
-          <t>300857</t>
+          <t>326120</t>
         </is>
       </c>
       <c r="T5" s="2" t="inlineStr">
         <is>
-          <t>324128</t>
+          <t>350779</t>
         </is>
       </c>
       <c r="U5" s="2" t="inlineStr">
         <is>
-          <t>83,99%</t>
+          <t>84,03%</t>
         </is>
       </c>
       <c r="V5" s="2" t="inlineStr">
         <is>
-          <t>80,5%</t>
+          <t>80,93%</t>
         </is>
       </c>
       <c r="W5" s="2" t="inlineStr">
         <is>
-          <t>86,73%</t>
+          <t>87,04%</t>
         </is>
       </c>
     </row>
@@ -5763,17 +5763,17 @@
       </c>
       <c r="D6" s="2" t="inlineStr">
         <is>
-          <t>136111</t>
+          <t>145674</t>
         </is>
       </c>
       <c r="E6" s="2" t="inlineStr">
         <is>
-          <t>136111</t>
+          <t>145674</t>
         </is>
       </c>
       <c r="F6" s="2" t="inlineStr">
         <is>
-          <t>136111</t>
+          <t>145674</t>
         </is>
       </c>
       <c r="G6" s="2" t="inlineStr">
@@ -5798,17 +5798,17 @@
       </c>
       <c r="K6" s="2" t="inlineStr">
         <is>
-          <t>237602</t>
+          <t>257315</t>
         </is>
       </c>
       <c r="L6" s="2" t="inlineStr">
         <is>
-          <t>237602</t>
+          <t>257315</t>
         </is>
       </c>
       <c r="M6" s="2" t="inlineStr">
         <is>
-          <t>237602</t>
+          <t>257315</t>
         </is>
       </c>
       <c r="N6" s="2" t="inlineStr">
@@ -5833,17 +5833,17 @@
       </c>
       <c r="R6" s="2" t="inlineStr">
         <is>
-          <t>373713</t>
+          <t>402988</t>
         </is>
       </c>
       <c r="S6" s="2" t="inlineStr">
         <is>
-          <t>373713</t>
+          <t>402988</t>
         </is>
       </c>
       <c r="T6" s="2" t="inlineStr">
         <is>
-          <t>373713</t>
+          <t>402988</t>
         </is>
       </c>
       <c r="U6" s="2" t="inlineStr">
@@ -5880,32 +5880,32 @@
       </c>
       <c r="D7" s="2" t="inlineStr">
         <is>
-          <t>87239</t>
+          <t>94828</t>
         </is>
       </c>
       <c r="E7" s="2" t="inlineStr">
         <is>
-          <t>70612</t>
+          <t>78202</t>
         </is>
       </c>
       <c r="F7" s="2" t="inlineStr">
         <is>
-          <t>104944</t>
+          <t>115470</t>
         </is>
       </c>
       <c r="G7" s="2" t="inlineStr">
         <is>
-          <t>23,6%</t>
+          <t>23,93%</t>
         </is>
       </c>
       <c r="H7" s="2" t="inlineStr">
         <is>
-          <t>19,1%</t>
+          <t>19,74%</t>
         </is>
       </c>
       <c r="I7" s="2" t="inlineStr">
         <is>
-          <t>28,39%</t>
+          <t>29,14%</t>
         </is>
       </c>
       <c r="J7" s="2" t="inlineStr">
@@ -5915,32 +5915,32 @@
       </c>
       <c r="K7" s="2" t="inlineStr">
         <is>
-          <t>112673</t>
+          <t>128997</t>
         </is>
       </c>
       <c r="L7" s="2" t="inlineStr">
         <is>
-          <t>75822</t>
+          <t>110521</t>
         </is>
       </c>
       <c r="M7" s="2" t="inlineStr">
         <is>
-          <t>140735</t>
+          <t>149161</t>
         </is>
       </c>
       <c r="N7" s="2" t="inlineStr">
         <is>
-          <t>22,46%</t>
+          <t>26,39%</t>
         </is>
       </c>
       <c r="O7" s="2" t="inlineStr">
         <is>
-          <t>15,12%</t>
+          <t>22,61%</t>
         </is>
       </c>
       <c r="P7" s="2" t="inlineStr">
         <is>
-          <t>28,06%</t>
+          <t>30,52%</t>
         </is>
       </c>
       <c r="Q7" s="2" t="inlineStr">
@@ -5950,32 +5950,32 @@
       </c>
       <c r="R7" s="2" t="inlineStr">
         <is>
-          <t>199912</t>
+          <t>223825</t>
         </is>
       </c>
       <c r="S7" s="2" t="inlineStr">
         <is>
-          <t>150360</t>
+          <t>199113</t>
         </is>
       </c>
       <c r="T7" s="2" t="inlineStr">
         <is>
-          <t>231549</t>
+          <t>249983</t>
         </is>
       </c>
       <c r="U7" s="2" t="inlineStr">
         <is>
-          <t>22,94%</t>
+          <t>25,29%</t>
         </is>
       </c>
       <c r="V7" s="2" t="inlineStr">
         <is>
-          <t>17,26%</t>
+          <t>22,5%</t>
         </is>
       </c>
       <c r="W7" s="2" t="inlineStr">
         <is>
-          <t>26,58%</t>
+          <t>28,25%</t>
         </is>
       </c>
     </row>
@@ -5993,32 +5993,32 @@
       </c>
       <c r="D8" s="2" t="inlineStr">
         <is>
-          <t>282419</t>
+          <t>301404</t>
         </is>
       </c>
       <c r="E8" s="2" t="inlineStr">
         <is>
-          <t>264714</t>
+          <t>280762</t>
         </is>
       </c>
       <c r="F8" s="2" t="inlineStr">
         <is>
-          <t>299046</t>
+          <t>318030</t>
         </is>
       </c>
       <c r="G8" s="2" t="inlineStr">
         <is>
-          <t>76,4%</t>
+          <t>76,07%</t>
         </is>
       </c>
       <c r="H8" s="2" t="inlineStr">
         <is>
-          <t>71,61%</t>
+          <t>70,86%</t>
         </is>
       </c>
       <c r="I8" s="2" t="inlineStr">
         <is>
-          <t>80,9%</t>
+          <t>80,26%</t>
         </is>
       </c>
       <c r="J8" s="2" t="inlineStr">
@@ -6028,32 +6028,32 @@
       </c>
       <c r="K8" s="2" t="inlineStr">
         <is>
-          <t>388943</t>
+          <t>359742</t>
         </is>
       </c>
       <c r="L8" s="2" t="inlineStr">
         <is>
-          <t>360881</t>
+          <t>339578</t>
         </is>
       </c>
       <c r="M8" s="2" t="inlineStr">
         <is>
-          <t>425794</t>
+          <t>378218</t>
         </is>
       </c>
       <c r="N8" s="2" t="inlineStr">
         <is>
-          <t>77,54%</t>
+          <t>73,61%</t>
         </is>
       </c>
       <c r="O8" s="2" t="inlineStr">
         <is>
-          <t>71,94%</t>
+          <t>69,48%</t>
         </is>
       </c>
       <c r="P8" s="2" t="inlineStr">
         <is>
-          <t>84,88%</t>
+          <t>77,39%</t>
         </is>
       </c>
       <c r="Q8" s="2" t="inlineStr">
@@ -6063,32 +6063,32 @@
       </c>
       <c r="R8" s="2" t="inlineStr">
         <is>
-          <t>671362</t>
+          <t>661146</t>
         </is>
       </c>
       <c r="S8" s="2" t="inlineStr">
         <is>
-          <t>639725</t>
+          <t>634988</t>
         </is>
       </c>
       <c r="T8" s="2" t="inlineStr">
         <is>
-          <t>720914</t>
+          <t>685858</t>
         </is>
       </c>
       <c r="U8" s="2" t="inlineStr">
         <is>
-          <t>77,06%</t>
+          <t>74,71%</t>
         </is>
       </c>
       <c r="V8" s="2" t="inlineStr">
         <is>
-          <t>73,42%</t>
+          <t>71,75%</t>
         </is>
       </c>
       <c r="W8" s="2" t="inlineStr">
         <is>
-          <t>82,74%</t>
+          <t>77,5%</t>
         </is>
       </c>
     </row>
@@ -6106,17 +6106,17 @@
       </c>
       <c r="D9" s="2" t="inlineStr">
         <is>
-          <t>369658</t>
+          <t>396232</t>
         </is>
       </c>
       <c r="E9" s="2" t="inlineStr">
         <is>
-          <t>369658</t>
+          <t>396232</t>
         </is>
       </c>
       <c r="F9" s="2" t="inlineStr">
         <is>
-          <t>369658</t>
+          <t>396232</t>
         </is>
       </c>
       <c r="G9" s="2" t="inlineStr">
@@ -6141,17 +6141,17 @@
       </c>
       <c r="K9" s="2" t="inlineStr">
         <is>
-          <t>501616</t>
+          <t>488739</t>
         </is>
       </c>
       <c r="L9" s="2" t="inlineStr">
         <is>
-          <t>501616</t>
+          <t>488739</t>
         </is>
       </c>
       <c r="M9" s="2" t="inlineStr">
         <is>
-          <t>501616</t>
+          <t>488739</t>
         </is>
       </c>
       <c r="N9" s="2" t="inlineStr">
@@ -6176,17 +6176,17 @@
       </c>
       <c r="R9" s="2" t="inlineStr">
         <is>
-          <t>871274</t>
+          <t>884971</t>
         </is>
       </c>
       <c r="S9" s="2" t="inlineStr">
         <is>
-          <t>871274</t>
+          <t>884971</t>
         </is>
       </c>
       <c r="T9" s="2" t="inlineStr">
         <is>
-          <t>871274</t>
+          <t>884971</t>
         </is>
       </c>
       <c r="U9" s="2" t="inlineStr">
@@ -6223,32 +6223,32 @@
       </c>
       <c r="D10" s="2" t="inlineStr">
         <is>
-          <t>39472</t>
+          <t>43853</t>
         </is>
       </c>
       <c r="E10" s="2" t="inlineStr">
         <is>
-          <t>29200</t>
+          <t>33218</t>
         </is>
       </c>
       <c r="F10" s="2" t="inlineStr">
         <is>
-          <t>50702</t>
+          <t>56130</t>
         </is>
       </c>
       <c r="G10" s="2" t="inlineStr">
         <is>
-          <t>29,82%</t>
+          <t>30,2%</t>
         </is>
       </c>
       <c r="H10" s="2" t="inlineStr">
         <is>
-          <t>22,06%</t>
+          <t>22,88%</t>
         </is>
       </c>
       <c r="I10" s="2" t="inlineStr">
         <is>
-          <t>38,31%</t>
+          <t>38,66%</t>
         </is>
       </c>
       <c r="J10" s="2" t="inlineStr">
@@ -6258,32 +6258,32 @@
       </c>
       <c r="K10" s="2" t="inlineStr">
         <is>
-          <t>47481</t>
+          <t>54408</t>
         </is>
       </c>
       <c r="L10" s="2" t="inlineStr">
         <is>
-          <t>37419</t>
+          <t>44380</t>
         </is>
       </c>
       <c r="M10" s="2" t="inlineStr">
         <is>
-          <t>57698</t>
+          <t>65480</t>
         </is>
       </c>
       <c r="N10" s="2" t="inlineStr">
         <is>
-          <t>30,94%</t>
+          <t>30,92%</t>
         </is>
       </c>
       <c r="O10" s="2" t="inlineStr">
         <is>
-          <t>24,38%</t>
+          <t>25,22%</t>
         </is>
       </c>
       <c r="P10" s="2" t="inlineStr">
         <is>
-          <t>37,6%</t>
+          <t>37,21%</t>
         </is>
       </c>
       <c r="Q10" s="2" t="inlineStr">
@@ -6293,32 +6293,32 @@
       </c>
       <c r="R10" s="2" t="inlineStr">
         <is>
-          <t>86952</t>
+          <t>98261</t>
         </is>
       </c>
       <c r="S10" s="2" t="inlineStr">
         <is>
-          <t>73080</t>
+          <t>82838</t>
         </is>
       </c>
       <c r="T10" s="2" t="inlineStr">
         <is>
-          <t>102233</t>
+          <t>114625</t>
         </is>
       </c>
       <c r="U10" s="2" t="inlineStr">
         <is>
-          <t>30,42%</t>
+          <t>30,6%</t>
         </is>
       </c>
       <c r="V10" s="2" t="inlineStr">
         <is>
-          <t>25,57%</t>
+          <t>25,79%</t>
         </is>
       </c>
       <c r="W10" s="2" t="inlineStr">
         <is>
-          <t>35,77%</t>
+          <t>35,69%</t>
         </is>
       </c>
     </row>
@@ -6336,32 +6336,32 @@
       </c>
       <c r="D11" s="2" t="inlineStr">
         <is>
-          <t>92884</t>
+          <t>101343</t>
         </is>
       </c>
       <c r="E11" s="2" t="inlineStr">
         <is>
-          <t>81654</t>
+          <t>89066</t>
         </is>
       </c>
       <c r="F11" s="2" t="inlineStr">
         <is>
-          <t>103156</t>
+          <t>111978</t>
         </is>
       </c>
       <c r="G11" s="2" t="inlineStr">
         <is>
-          <t>70,18%</t>
+          <t>69,8%</t>
         </is>
       </c>
       <c r="H11" s="2" t="inlineStr">
         <is>
-          <t>61,69%</t>
+          <t>61,34%</t>
         </is>
       </c>
       <c r="I11" s="2" t="inlineStr">
         <is>
-          <t>77,94%</t>
+          <t>77,12%</t>
         </is>
       </c>
       <c r="J11" s="2" t="inlineStr">
@@ -6371,32 +6371,32 @@
       </c>
       <c r="K11" s="2" t="inlineStr">
         <is>
-          <t>105975</t>
+          <t>121544</t>
         </is>
       </c>
       <c r="L11" s="2" t="inlineStr">
         <is>
-          <t>95758</t>
+          <t>110472</t>
         </is>
       </c>
       <c r="M11" s="2" t="inlineStr">
         <is>
-          <t>116037</t>
+          <t>131572</t>
         </is>
       </c>
       <c r="N11" s="2" t="inlineStr">
         <is>
-          <t>69,06%</t>
+          <t>69,08%</t>
         </is>
       </c>
       <c r="O11" s="2" t="inlineStr">
         <is>
-          <t>62,4%</t>
+          <t>62,79%</t>
         </is>
       </c>
       <c r="P11" s="2" t="inlineStr">
         <is>
-          <t>75,62%</t>
+          <t>74,78%</t>
         </is>
       </c>
       <c r="Q11" s="2" t="inlineStr">
@@ -6406,32 +6406,32 @@
       </c>
       <c r="R11" s="2" t="inlineStr">
         <is>
-          <t>198860</t>
+          <t>222887</t>
         </is>
       </c>
       <c r="S11" s="2" t="inlineStr">
         <is>
-          <t>183579</t>
+          <t>206523</t>
         </is>
       </c>
       <c r="T11" s="2" t="inlineStr">
         <is>
-          <t>212732</t>
+          <t>238310</t>
         </is>
       </c>
       <c r="U11" s="2" t="inlineStr">
         <is>
-          <t>69,58%</t>
+          <t>69,4%</t>
         </is>
       </c>
       <c r="V11" s="2" t="inlineStr">
         <is>
-          <t>64,23%</t>
+          <t>64,31%</t>
         </is>
       </c>
       <c r="W11" s="2" t="inlineStr">
         <is>
-          <t>74,43%</t>
+          <t>74,21%</t>
         </is>
       </c>
     </row>
@@ -6449,17 +6449,17 @@
       </c>
       <c r="D12" s="2" t="inlineStr">
         <is>
-          <t>132356</t>
+          <t>145196</t>
         </is>
       </c>
       <c r="E12" s="2" t="inlineStr">
         <is>
-          <t>132356</t>
+          <t>145196</t>
         </is>
       </c>
       <c r="F12" s="2" t="inlineStr">
         <is>
-          <t>132356</t>
+          <t>145196</t>
         </is>
       </c>
       <c r="G12" s="2" t="inlineStr">
@@ -6484,17 +6484,17 @@
       </c>
       <c r="K12" s="2" t="inlineStr">
         <is>
-          <t>153456</t>
+          <t>175952</t>
         </is>
       </c>
       <c r="L12" s="2" t="inlineStr">
         <is>
-          <t>153456</t>
+          <t>175952</t>
         </is>
       </c>
       <c r="M12" s="2" t="inlineStr">
         <is>
-          <t>153456</t>
+          <t>175952</t>
         </is>
       </c>
       <c r="N12" s="2" t="inlineStr">
@@ -6519,17 +6519,17 @@
       </c>
       <c r="R12" s="2" t="inlineStr">
         <is>
-          <t>285812</t>
+          <t>321148</t>
         </is>
       </c>
       <c r="S12" s="2" t="inlineStr">
         <is>
-          <t>285812</t>
+          <t>321148</t>
         </is>
       </c>
       <c r="T12" s="2" t="inlineStr">
         <is>
-          <t>285812</t>
+          <t>321148</t>
         </is>
       </c>
       <c r="U12" s="2" t="inlineStr">
@@ -6566,32 +6566,32 @@
       </c>
       <c r="D13" s="2" t="inlineStr">
         <is>
-          <t>153800</t>
+          <t>167311</t>
         </is>
       </c>
       <c r="E13" s="2" t="inlineStr">
         <is>
-          <t>132347</t>
+          <t>145923</t>
         </is>
       </c>
       <c r="F13" s="2" t="inlineStr">
         <is>
-          <t>179585</t>
+          <t>192147</t>
         </is>
       </c>
       <c r="G13" s="2" t="inlineStr">
         <is>
-          <t>24,1%</t>
+          <t>24,35%</t>
         </is>
       </c>
       <c r="H13" s="2" t="inlineStr">
         <is>
-          <t>20,74%</t>
+          <t>21,24%</t>
         </is>
       </c>
       <c r="I13" s="2" t="inlineStr">
         <is>
-          <t>28,14%</t>
+          <t>27,96%</t>
         </is>
       </c>
       <c r="J13" s="2" t="inlineStr">
@@ -6601,32 +6601,32 @@
       </c>
       <c r="K13" s="2" t="inlineStr">
         <is>
-          <t>192908</t>
+          <t>219119</t>
         </is>
       </c>
       <c r="L13" s="2" t="inlineStr">
         <is>
-          <t>148122</t>
+          <t>196542</t>
         </is>
       </c>
       <c r="M13" s="2" t="inlineStr">
         <is>
-          <t>218974</t>
+          <t>244723</t>
         </is>
       </c>
       <c r="N13" s="2" t="inlineStr">
         <is>
-          <t>21,61%</t>
+          <t>23,77%</t>
         </is>
       </c>
       <c r="O13" s="2" t="inlineStr">
         <is>
-          <t>16,59%</t>
+          <t>21,32%</t>
         </is>
       </c>
       <c r="P13" s="2" t="inlineStr">
         <is>
-          <t>24,53%</t>
+          <t>26,54%</t>
         </is>
       </c>
       <c r="Q13" s="2" t="inlineStr">
@@ -6636,32 +6636,32 @@
       </c>
       <c r="R13" s="2" t="inlineStr">
         <is>
-          <t>346709</t>
+          <t>386429</t>
         </is>
       </c>
       <c r="S13" s="2" t="inlineStr">
         <is>
-          <t>294403</t>
+          <t>355484</t>
         </is>
       </c>
       <c r="T13" s="2" t="inlineStr">
         <is>
-          <t>379586</t>
+          <t>420526</t>
         </is>
       </c>
       <c r="U13" s="2" t="inlineStr">
         <is>
-          <t>22,65%</t>
+          <t>24,02%</t>
         </is>
       </c>
       <c r="V13" s="2" t="inlineStr">
         <is>
-          <t>19,23%</t>
+          <t>22,09%</t>
         </is>
       </c>
       <c r="W13" s="2" t="inlineStr">
         <is>
-          <t>24,8%</t>
+          <t>26,13%</t>
         </is>
       </c>
     </row>
@@ -6679,32 +6679,32 @@
       </c>
       <c r="D14" s="2" t="inlineStr">
         <is>
-          <t>484325</t>
+          <t>519791</t>
         </is>
       </c>
       <c r="E14" s="2" t="inlineStr">
         <is>
-          <t>458540</t>
+          <t>494955</t>
         </is>
       </c>
       <c r="F14" s="2" t="inlineStr">
         <is>
-          <t>505778</t>
+          <t>541179</t>
         </is>
       </c>
       <c r="G14" s="2" t="inlineStr">
         <is>
-          <t>75,9%</t>
+          <t>75,65%</t>
         </is>
       </c>
       <c r="H14" s="2" t="inlineStr">
         <is>
-          <t>71,86%</t>
+          <t>72,04%</t>
         </is>
       </c>
       <c r="I14" s="2" t="inlineStr">
         <is>
-          <t>79,26%</t>
+          <t>78,76%</t>
         </is>
       </c>
       <c r="J14" s="2" t="inlineStr">
@@ -6714,32 +6714,32 @@
       </c>
       <c r="K14" s="2" t="inlineStr">
         <is>
-          <t>699766</t>
+          <t>702887</t>
         </is>
       </c>
       <c r="L14" s="2" t="inlineStr">
         <is>
-          <t>673700</t>
+          <t>677283</t>
         </is>
       </c>
       <c r="M14" s="2" t="inlineStr">
         <is>
-          <t>744552</t>
+          <t>725464</t>
         </is>
       </c>
       <c r="N14" s="2" t="inlineStr">
         <is>
-          <t>78,39%</t>
+          <t>76,23%</t>
         </is>
       </c>
       <c r="O14" s="2" t="inlineStr">
         <is>
-          <t>75,47%</t>
+          <t>73,46%</t>
         </is>
       </c>
       <c r="P14" s="2" t="inlineStr">
         <is>
-          <t>83,41%</t>
+          <t>78,68%</t>
         </is>
       </c>
       <c r="Q14" s="2" t="inlineStr">
@@ -6749,32 +6749,32 @@
       </c>
       <c r="R14" s="2" t="inlineStr">
         <is>
-          <t>1184091</t>
+          <t>1222678</t>
         </is>
       </c>
       <c r="S14" s="2" t="inlineStr">
         <is>
-          <t>1151214</t>
+          <t>1188581</t>
         </is>
       </c>
       <c r="T14" s="2" t="inlineStr">
         <is>
-          <t>1236397</t>
+          <t>1253623</t>
         </is>
       </c>
       <c r="U14" s="2" t="inlineStr">
         <is>
-          <t>77,35%</t>
+          <t>75,98%</t>
         </is>
       </c>
       <c r="V14" s="2" t="inlineStr">
         <is>
-          <t>75,2%</t>
+          <t>73,87%</t>
         </is>
       </c>
       <c r="W14" s="2" t="inlineStr">
         <is>
-          <t>80,77%</t>
+          <t>77,91%</t>
         </is>
       </c>
     </row>
@@ -6792,17 +6792,17 @@
       </c>
       <c r="D15" s="2" t="inlineStr">
         <is>
-          <t>638125</t>
+          <t>687102</t>
         </is>
       </c>
       <c r="E15" s="2" t="inlineStr">
         <is>
-          <t>638125</t>
+          <t>687102</t>
         </is>
       </c>
       <c r="F15" s="2" t="inlineStr">
         <is>
-          <t>638125</t>
+          <t>687102</t>
         </is>
       </c>
       <c r="G15" s="2" t="inlineStr">
@@ -6827,17 +6827,17 @@
       </c>
       <c r="K15" s="2" t="inlineStr">
         <is>
-          <t>892674</t>
+          <t>922006</t>
         </is>
       </c>
       <c r="L15" s="2" t="inlineStr">
         <is>
-          <t>892674</t>
+          <t>922006</t>
         </is>
       </c>
       <c r="M15" s="2" t="inlineStr">
         <is>
-          <t>892674</t>
+          <t>922006</t>
         </is>
       </c>
       <c r="N15" s="2" t="inlineStr">
@@ -6862,17 +6862,17 @@
       </c>
       <c r="R15" s="2" t="inlineStr">
         <is>
-          <t>1530800</t>
+          <t>1609107</t>
         </is>
       </c>
       <c r="S15" s="2" t="inlineStr">
         <is>
-          <t>1530800</t>
+          <t>1609107</t>
         </is>
       </c>
       <c r="T15" s="2" t="inlineStr">
         <is>
-          <t>1530800</t>
+          <t>1609107</t>
         </is>
       </c>
       <c r="U15" s="2" t="inlineStr">

--- a/data/trans_orig/P17E-Estudios-trans_orig.xlsx
+++ b/data/trans_orig/P17E-Estudios-trans_orig.xlsx
@@ -718,7 +718,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -831,7 +831,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -1061,7 +1061,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -1174,7 +1174,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -1404,7 +1404,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -1517,7 +1517,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -1747,7 +1747,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -1860,7 +1860,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -2321,7 +2321,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -2434,7 +2434,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -2664,7 +2664,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -2777,7 +2777,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -3007,7 +3007,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -3120,7 +3120,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -3350,7 +3350,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -3463,7 +3463,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -3924,7 +3924,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -4037,7 +4037,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -4267,7 +4267,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -4380,7 +4380,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -4610,7 +4610,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -4723,7 +4723,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -4953,7 +4953,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -5066,7 +5066,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
@@ -5527,7 +5527,7 @@
       </c>
       <c r="B4" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C4" s="2" t="inlineStr">
@@ -5640,7 +5640,7 @@
       <c r="A5" s="1" t="n"/>
       <c r="B5" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C5" s="2" t="inlineStr">
@@ -5870,7 +5870,7 @@
       </c>
       <c r="B7" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C7" s="2" t="inlineStr">
@@ -5983,7 +5983,7 @@
       <c r="A8" s="1" t="n"/>
       <c r="B8" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C8" s="2" t="inlineStr">
@@ -6213,7 +6213,7 @@
       </c>
       <c r="B10" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C10" s="2" t="inlineStr">
@@ -6326,7 +6326,7 @@
       <c r="A11" s="1" t="n"/>
       <c r="B11" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C11" s="2" t="inlineStr">
@@ -6556,7 +6556,7 @@
       </c>
       <c r="B13" s="3" t="inlineStr">
         <is>
-          <t>Otros</t>
+          <t>Otras Especialidades</t>
         </is>
       </c>
       <c r="C13" s="2" t="inlineStr">
@@ -6669,7 +6669,7 @@
       <c r="A14" s="1" t="n"/>
       <c r="B14" s="3" t="inlineStr">
         <is>
-          <t>Médico general</t>
+          <t>Especialista Medicina Familiar y Comunitaria</t>
         </is>
       </c>
       <c r="C14" s="2" t="inlineStr">
